--- a/trades/by_strategy/trendline_reversal.xlsx
+++ b/trades/by_strategy/trendline_reversal.xlsx
@@ -538,7 +538,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22750 PE</t>
+          <t>NIFTY 22650 PE</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
@@ -870,28 +870,28 @@
         </is>
       </c>
       <c r="R3" s="11" t="n">
-        <v>224.12</v>
+        <v>176.29</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>253.31</v>
+        <v>201.28</v>
       </c>
       <c r="T3" s="13" t="n">
-        <v>14568</v>
+        <v>45835</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>16465</v>
+        <v>52333</v>
       </c>
       <c r="V3" s="14" t="n">
-        <v>1820</v>
+        <v>6356</v>
       </c>
       <c r="W3" s="15" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z3" s="10" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>208.75</v>
+        <v>164.2</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>208.59</v>
+        <v>164.05</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>27138</v>
+        <v>42692</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>27117</v>
+        <v>42653</v>
       </c>
       <c r="V4" s="17" t="n">
-        <v>-118</v>
+        <v>-166</v>
       </c>
       <c r="W4" s="18" t="n">
         <v>-0.4</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>74.59999999999999</v>
+        <v>37.68</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>74.09</v>
+        <v>37.25</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>4849</v>
+        <v>7348</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>4816</v>
+        <v>7264</v>
       </c>
       <c r="V5" s="20" t="n">
-        <v>-89</v>
+        <v>-145</v>
       </c>
       <c r="W5" s="21" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z5" s="10" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23100 PE</t>
+          <t>NIFTY 23000 PE</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1176,28 +1176,28 @@
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>120.83</v>
+        <v>76.78</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>99.56</v>
+        <v>61.28</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>7854</v>
+        <v>9981</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>6471</v>
+        <v>7966</v>
       </c>
       <c r="V6" s="17" t="n">
-        <v>-1442</v>
+        <v>-2078</v>
       </c>
       <c r="W6" s="18" t="n">
-        <v>-18.4</v>
+        <v>-20.8</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23000 CE</t>
+          <t>NIFTY 23100 CE</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="R7" s="11" t="n">
-        <v>130.47</v>
+        <v>89.03</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>159.04</v>
+        <v>111.19</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>16961</v>
+        <v>11574</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>20675</v>
+        <v>14455</v>
       </c>
       <c r="V7" s="14" t="n">
-        <v>3630</v>
+        <v>2808</v>
       </c>
       <c r="W7" s="15" t="n">
-        <v>21.4</v>
+        <v>24.3</v>
       </c>
       <c r="X7" s="9" t="n">
         <v>2</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22750 CE</t>
+          <t>NIFTY 22850 CE</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>150.07</v>
+        <v>106.13</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>132.38</v>
+        <v>92.19</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>19509</v>
+        <v>13797</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>17209</v>
+        <v>11985</v>
       </c>
       <c r="V8" s="17" t="n">
-        <v>-2380</v>
+        <v>-1882</v>
       </c>
       <c r="W8" s="18" t="n">
-        <v>-12.2</v>
+        <v>-13.6</v>
       </c>
       <c r="X8" s="2" t="n">
         <v>2</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22550 CE</t>
+          <t>NIFTY 22650 CE</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
@@ -1482,28 +1482,28 @@
         </is>
       </c>
       <c r="R9" s="11" t="n">
-        <v>181.07</v>
+        <v>135.25</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>164.99</v>
+        <v>122.03</v>
       </c>
       <c r="T9" s="13" t="n">
-        <v>23539</v>
+        <v>35165</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>21449</v>
+        <v>31728</v>
       </c>
       <c r="V9" s="20" t="n">
-        <v>-2178</v>
+        <v>-3545</v>
       </c>
       <c r="W9" s="21" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z9" s="10" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22350 PE</t>
+          <t>NIFTY 22250 PE</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1584,28 +1584,28 @@
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>63.9</v>
+        <v>27.58</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>90.19</v>
+        <v>42.06</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>4154</v>
+        <v>5378</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>5862</v>
+        <v>8202</v>
       </c>
       <c r="V10" s="7" t="n">
-        <v>1652</v>
+        <v>2762</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>39.8</v>
+        <v>51.4</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22550 CE</t>
+          <t>NIFTY 22650 CE</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
@@ -1686,22 +1686,22 @@
         </is>
       </c>
       <c r="R11" s="11" t="n">
-        <v>133.51</v>
+        <v>91.84</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>145.48</v>
+        <v>101.07</v>
       </c>
       <c r="T11" s="13" t="n">
-        <v>17356</v>
+        <v>11939</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>18912</v>
+        <v>13139</v>
       </c>
       <c r="V11" s="14" t="n">
-        <v>1474</v>
+        <v>1129</v>
       </c>
       <c r="W11" s="15" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="X11" s="9" t="n">
         <v>2</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22500 PE</t>
+          <t>NIFTY 22400 PE</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1788,22 +1788,22 @@
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>153.06</v>
+        <v>106.72</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>152.75</v>
+        <v>106.42</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>19898</v>
+        <v>13874</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>19858</v>
+        <v>13835</v>
       </c>
       <c r="V12" s="17" t="n">
-        <v>-124</v>
+        <v>-112</v>
       </c>
       <c r="W12" s="18" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="X12" s="2" t="n">
         <v>2</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 22350 PE</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
@@ -1890,28 +1890,28 @@
         </is>
       </c>
       <c r="R13" s="11" t="n">
-        <v>143.4</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>212.88</v>
+        <v>155.48</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>9321</v>
+        <v>12940</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>13837</v>
+        <v>20212</v>
       </c>
       <c r="V13" s="14" t="n">
-        <v>4445</v>
+        <v>7191</v>
       </c>
       <c r="W13" s="15" t="n">
-        <v>47.7</v>
+        <v>55.6</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z13" s="10" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22650 PE</t>
+          <t>NIFTY 22550 PE</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1992,28 +1992,28 @@
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>147.39</v>
+        <v>104.46</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>191.43</v>
+        <v>139.92</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>9580</v>
+        <v>13580</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>12443</v>
+        <v>18190</v>
       </c>
       <c r="V14" s="7" t="n">
-        <v>2794</v>
+        <v>4531</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>29.2</v>
+        <v>33.4</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22700 PE</t>
+          <t>NIFTY 22600 PE</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2196,28 +2196,28 @@
         </is>
       </c>
       <c r="R16" s="4" t="n">
-        <v>191.03</v>
+        <v>144.03</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>180.84</v>
+        <v>135.53</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>24834</v>
+        <v>37448</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>23509</v>
+        <v>35238</v>
       </c>
       <c r="V16" s="17" t="n">
-        <v>-1416</v>
+        <v>-2324</v>
       </c>
       <c r="W16" s="18" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22650 CE</t>
+          <t>NIFTY 22750 CE</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
@@ -2298,28 +2298,28 @@
         </is>
       </c>
       <c r="R17" s="11" t="n">
-        <v>198</v>
+        <v>150.92</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>217.48</v>
+        <v>167.14</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>25740</v>
+        <v>39239</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>28272</v>
+        <v>43456</v>
       </c>
       <c r="V17" s="14" t="n">
-        <v>2434</v>
+        <v>4091</v>
       </c>
       <c r="W17" s="15" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="X17" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z17" s="10" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22550 CE</t>
+          <t>NIFTY 22650 CE</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2400,22 +2400,22 @@
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>148.73</v>
+        <v>103.57</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>131.57</v>
+        <v>90.12</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>19335</v>
+        <v>13464</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>17104</v>
+        <v>11716</v>
       </c>
       <c r="V18" s="17" t="n">
-        <v>-2311</v>
+        <v>-1818</v>
       </c>
       <c r="W18" s="18" t="n">
-        <v>-12</v>
+        <v>-13.5</v>
       </c>
       <c r="X18" s="2" t="n">
         <v>2</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr">
@@ -2502,22 +2502,22 @@
         </is>
       </c>
       <c r="R19" s="11" t="n">
-        <v>145.75</v>
+        <v>100.66</v>
       </c>
       <c r="S19" s="11" t="n">
-        <v>210.12</v>
+        <v>152.27</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>18948</v>
+        <v>13086</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>27316</v>
+        <v>19795</v>
       </c>
       <c r="V19" s="14" t="n">
-        <v>8274</v>
+        <v>6628</v>
       </c>
       <c r="W19" s="15" t="n">
-        <v>43.7</v>
+        <v>50.6</v>
       </c>
       <c r="X19" s="9" t="n">
         <v>2</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22700 PE</t>
+          <t>NIFTY 22600 PE</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="R20" s="4" t="n">
-        <v>152.21</v>
+        <v>107.79</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>181.1</v>
+        <v>130.95</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>19787</v>
+        <v>14013</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>23543</v>
+        <v>17024</v>
       </c>
       <c r="V20" s="7" t="n">
-        <v>3666</v>
+        <v>2933</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>18.5</v>
+        <v>20.9</v>
       </c>
       <c r="X20" s="2" t="n">
         <v>2</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22750 CE</t>
+          <t>NIFTY 22850 CE</t>
         </is>
       </c>
       <c r="Q21" s="9" t="inlineStr">
@@ -2706,22 +2706,22 @@
         </is>
       </c>
       <c r="R21" s="11" t="n">
-        <v>151.47</v>
+        <v>108.11</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>171.99</v>
+        <v>124.5</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>19691</v>
+        <v>14054</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>22359</v>
+        <v>16185</v>
       </c>
       <c r="V21" s="14" t="n">
-        <v>2580</v>
+        <v>2054</v>
       </c>
       <c r="W21" s="15" t="n">
-        <v>13.1</v>
+        <v>14.6</v>
       </c>
       <c r="X21" s="9" t="n">
         <v>2</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2808,28 +2808,28 @@
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>179.32</v>
+        <v>133.1</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>257.48</v>
+        <v>198.78</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>23312</v>
+        <v>34606</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>33472</v>
+        <v>51683</v>
       </c>
       <c r="V22" s="7" t="n">
-        <v>10056</v>
+        <v>16941</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>43.1</v>
+        <v>49</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23050 PE</t>
+          <t>NIFTY 22950 PE</t>
         </is>
       </c>
       <c r="Q23" s="9" t="inlineStr">
@@ -2910,22 +2910,22 @@
         </is>
       </c>
       <c r="R23" s="11" t="n">
-        <v>120.57</v>
+        <v>77.53</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>102.05</v>
+        <v>63.82</v>
       </c>
       <c r="T23" s="13" t="n">
-        <v>15674</v>
+        <v>10079</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>13266</v>
+        <v>8297</v>
       </c>
       <c r="V23" s="20" t="n">
-        <v>-2481</v>
+        <v>-1846</v>
       </c>
       <c r="W23" s="21" t="n">
-        <v>-15.8</v>
+        <v>-18.3</v>
       </c>
       <c r="X23" s="9" t="n">
         <v>2</v>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23200 PE</t>
+          <t>NIFTY 23100 PE</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3012,28 +3012,28 @@
         </is>
       </c>
       <c r="R24" s="4" t="n">
-        <v>110.24</v>
+        <v>67.95</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>182.03</v>
+        <v>122.17</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>7166</v>
+        <v>8834</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>11832</v>
+        <v>15882</v>
       </c>
       <c r="V24" s="7" t="n">
-        <v>4599</v>
+        <v>6975</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>64.2</v>
+        <v>79</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23250 CE</t>
+          <t>NIFTY 23350 CE</t>
         </is>
       </c>
       <c r="Q25" s="9" t="inlineStr">
@@ -3114,28 +3114,28 @@
         </is>
       </c>
       <c r="R25" s="11" t="n">
-        <v>108.09</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>93.42</v>
+        <v>56.45</v>
       </c>
       <c r="T25" s="13" t="n">
-        <v>14052</v>
+        <v>13057</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>12145</v>
+        <v>11008</v>
       </c>
       <c r="V25" s="20" t="n">
-        <v>-1978</v>
+        <v>-2118</v>
       </c>
       <c r="W25" s="21" t="n">
-        <v>-14.1</v>
+        <v>-16.2</v>
       </c>
       <c r="X25" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y25" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z25" s="10" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23400 CE</t>
+          <t>NIFTY 23500 CE</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3216,28 +3216,28 @@
         </is>
       </c>
       <c r="R26" s="4" t="n">
-        <v>130.68</v>
+        <v>87.63</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>161.81</v>
+        <v>111.64</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>8494</v>
+        <v>11392</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>10518</v>
+        <v>14513</v>
       </c>
       <c r="V26" s="7" t="n">
-        <v>1958</v>
+        <v>3049</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>23.1</v>
+        <v>26.8</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23350 PE</t>
+          <t>NIFTY 23250 PE</t>
         </is>
       </c>
       <c r="Q27" s="9" t="inlineStr">
@@ -3318,28 +3318,28 @@
         </is>
       </c>
       <c r="R27" s="11" t="n">
-        <v>156.65</v>
+        <v>109.47</v>
       </c>
       <c r="S27" s="11" t="n">
-        <v>156.47</v>
+        <v>109.3</v>
       </c>
       <c r="T27" s="13" t="n">
-        <v>20364</v>
+        <v>28462</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>20341</v>
+        <v>28418</v>
       </c>
       <c r="V27" s="20" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="W27" s="21" t="n">
         <v>-0.5</v>
       </c>
       <c r="X27" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z27" s="10" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23400 CE</t>
+          <t>NIFTY 23500 CE</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3420,28 +3420,28 @@
         </is>
       </c>
       <c r="R28" s="4" t="n">
-        <v>70.81999999999999</v>
+        <v>27.92</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>76.91</v>
+        <v>30.45</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>9207</v>
+        <v>5444</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>9998</v>
+        <v>5938</v>
       </c>
       <c r="V28" s="7" t="n">
-        <v>726</v>
+        <v>435</v>
       </c>
       <c r="W28" s="8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23350 CE</t>
+          <t>NIFTY 23450 CE</t>
         </is>
       </c>
       <c r="Q29" s="9" t="inlineStr">
@@ -3522,28 +3522,28 @@
         </is>
       </c>
       <c r="R29" s="11" t="n">
-        <v>111.83</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>121.24</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="T29" s="13" t="n">
-        <v>14538</v>
+        <v>13837</v>
       </c>
       <c r="U29" s="13" t="n">
-        <v>15761</v>
+        <v>15163</v>
       </c>
       <c r="V29" s="14" t="n">
-        <v>1147</v>
+        <v>1251</v>
       </c>
       <c r="W29" s="15" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z29" s="10" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23300 PE</t>
+          <t>NIFTY 23200 PE</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="R30" s="4" t="n">
-        <v>119.36</v>
+        <v>76.41</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>103.78</v>
+        <v>64.75</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>15517</v>
+        <v>14900</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>13491</v>
+        <v>12626</v>
       </c>
       <c r="V30" s="17" t="n">
-        <v>-2099</v>
+        <v>-2345</v>
       </c>
       <c r="W30" s="18" t="n">
-        <v>-13.5</v>
+        <v>-15.7</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23300 CE</t>
+          <t>NIFTY 23400 CE</t>
         </is>
       </c>
       <c r="Q31" s="9" t="inlineStr">
@@ -3726,28 +3726,28 @@
         </is>
       </c>
       <c r="R31" s="11" t="n">
-        <v>133.81</v>
+        <v>92.11</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>163.85</v>
+        <v>115.65</v>
       </c>
       <c r="T31" s="13" t="n">
-        <v>8698</v>
+        <v>11974</v>
       </c>
       <c r="U31" s="13" t="n">
-        <v>10650</v>
+        <v>15034</v>
       </c>
       <c r="V31" s="14" t="n">
-        <v>1886</v>
+        <v>2986</v>
       </c>
       <c r="W31" s="15" t="n">
-        <v>21.7</v>
+        <v>24.9</v>
       </c>
       <c r="X31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y31" s="9" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z31" s="10" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23250 PE</t>
+          <t>NIFTY 23150 PE</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3828,28 +3828,28 @@
         </is>
       </c>
       <c r="R32" s="4" t="n">
-        <v>151.42</v>
+        <v>105.29</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>126.59</v>
+        <v>85.92</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>9842</v>
+        <v>13688</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>8228</v>
+        <v>11170</v>
       </c>
       <c r="V32" s="17" t="n">
-        <v>-1677</v>
+        <v>-2587</v>
       </c>
       <c r="W32" s="18" t="n">
-        <v>-17</v>
+        <v>-18.9</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23350 PE</t>
+          <t>NIFTY 23250 PE</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4032,28 +4032,28 @@
         </is>
       </c>
       <c r="R34" s="4" t="n">
-        <v>171.87</v>
+        <v>124.18</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>201.47</v>
+        <v>148.27</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>22343</v>
+        <v>32287</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>26191</v>
+        <v>38550</v>
       </c>
       <c r="V34" s="7" t="n">
-        <v>3754</v>
+        <v>6147</v>
       </c>
       <c r="W34" s="8" t="n">
-        <v>16.8</v>
+        <v>19</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23450 PE</t>
+          <t>NIFTY 23350 PE</t>
         </is>
       </c>
       <c r="Q35" s="9" t="inlineStr">
@@ -4134,22 +4134,22 @@
         </is>
       </c>
       <c r="R35" s="11" t="n">
-        <v>138.02</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>162.15</v>
+        <v>110.78</v>
       </c>
       <c r="T35" s="13" t="n">
-        <v>17943</v>
+        <v>11998</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>21080</v>
+        <v>14401</v>
       </c>
       <c r="V35" s="14" t="n">
-        <v>3052</v>
+        <v>2331</v>
       </c>
       <c r="W35" s="15" t="n">
-        <v>17</v>
+        <v>19.4</v>
       </c>
       <c r="X35" s="9" t="n">
         <v>2</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23450 CE</t>
+          <t>NIFTY 23550 CE</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4236,28 +4236,28 @@
         </is>
       </c>
       <c r="R36" s="4" t="n">
-        <v>123.54</v>
+        <v>81.92</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>122.83</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>16060</v>
+        <v>15974</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>15968</v>
+        <v>15842</v>
       </c>
       <c r="V36" s="17" t="n">
-        <v>-169</v>
+        <v>-209</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23500 PE</t>
+          <t>NIFTY 23400 PE</t>
         </is>
       </c>
       <c r="Q37" s="9" t="inlineStr">
@@ -4338,22 +4338,22 @@
         </is>
       </c>
       <c r="R37" s="11" t="n">
-        <v>135.49</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>118.59</v>
+        <v>78.37</v>
       </c>
       <c r="T37" s="13" t="n">
-        <v>17614</v>
+        <v>11864</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>15417</v>
+        <v>10188</v>
       </c>
       <c r="V37" s="20" t="n">
-        <v>-2274</v>
+        <v>-1743</v>
       </c>
       <c r="W37" s="21" t="n">
-        <v>-12.9</v>
+        <v>-14.7</v>
       </c>
       <c r="X37" s="9" t="n">
         <v>2</v>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23650 PE</t>
+          <t>NIFTY 23550 PE</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4440,28 +4440,28 @@
         </is>
       </c>
       <c r="R38" s="4" t="n">
-        <v>137.87</v>
+        <v>95.08</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>147.31</v>
+        <v>102.14</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>17923</v>
+        <v>24721</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>19150</v>
+        <v>26556</v>
       </c>
       <c r="V38" s="7" t="n">
-        <v>1145</v>
+        <v>1740</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23950 PE</t>
+          <t>NIFTY 23850 PE</t>
         </is>
       </c>
       <c r="Q39" s="9" t="inlineStr">
@@ -4542,22 +4542,22 @@
         </is>
       </c>
       <c r="R39" s="11" t="n">
-        <v>110.95</v>
+        <v>68.78</v>
       </c>
       <c r="S39" s="11" t="n">
-        <v>119.39</v>
+        <v>74.52</v>
       </c>
       <c r="T39" s="13" t="n">
-        <v>14424</v>
+        <v>8941</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>15521</v>
+        <v>9688</v>
       </c>
       <c r="V39" s="14" t="n">
-        <v>1022</v>
+        <v>681</v>
       </c>
       <c r="W39" s="15" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="X39" s="9" t="n">
         <v>2</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23850 CE</t>
+          <t>NIFTY 23950 CE</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4644,28 +4644,28 @@
         </is>
       </c>
       <c r="R40" s="4" t="n">
-        <v>135.96</v>
+        <v>93.11</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>160.27</v>
+        <v>111.95</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>8837</v>
+        <v>12104</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>10418</v>
+        <v>14554</v>
       </c>
       <c r="V40" s="7" t="n">
-        <v>1514</v>
+        <v>2376</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>17.1</v>
+        <v>19.6</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24100 PE</t>
+          <t>NIFTY 24000 PE</t>
         </is>
       </c>
       <c r="Q41" s="9" t="inlineStr">
@@ -4746,28 +4746,28 @@
         </is>
       </c>
       <c r="R41" s="11" t="n">
-        <v>153.38</v>
+        <v>107.67</v>
       </c>
       <c r="S41" s="11" t="n">
-        <v>172.31</v>
+        <v>122.74</v>
       </c>
       <c r="T41" s="13" t="n">
-        <v>19939</v>
+        <v>27994</v>
       </c>
       <c r="U41" s="13" t="n">
-        <v>22400</v>
+        <v>31912</v>
       </c>
       <c r="V41" s="14" t="n">
-        <v>2373</v>
+        <v>3813</v>
       </c>
       <c r="W41" s="15" t="n">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="X41" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y41" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z41" s="10" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24150 CE</t>
+          <t>NIFTY 24250 CE</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4848,22 +4848,22 @@
         </is>
       </c>
       <c r="R42" s="4" t="n">
-        <v>133.16</v>
+        <v>86.78</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>113.45</v>
+        <v>71.98</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>17311</v>
+        <v>11281</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>14748</v>
+        <v>9357</v>
       </c>
       <c r="V42" s="17" t="n">
-        <v>-2638</v>
+        <v>-1989</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>-15.2</v>
+        <v>-17.6</v>
       </c>
       <c r="X42" s="2" t="n">
         <v>2</v>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24200 CE</t>
+          <t>NIFTY 24300 CE</t>
         </is>
       </c>
       <c r="Q43" s="9" t="inlineStr">
@@ -4950,28 +4950,28 @@
         </is>
       </c>
       <c r="R43" s="11" t="n">
-        <v>143.72</v>
+        <v>101.43</v>
       </c>
       <c r="S43" s="11" t="n">
-        <v>180</v>
+        <v>130.46</v>
       </c>
       <c r="T43" s="13" t="n">
-        <v>9342</v>
+        <v>26372</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>11700</v>
+        <v>33920</v>
       </c>
       <c r="V43" s="14" t="n">
-        <v>2290</v>
+        <v>7441</v>
       </c>
       <c r="W43" s="15" t="n">
-        <v>24.5</v>
+        <v>28.2</v>
       </c>
       <c r="X43" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y43" s="9" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z43" s="10" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24300 CE</t>
+          <t>NIFTY 24400 CE</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5052,28 +5052,28 @@
         </is>
       </c>
       <c r="R44" s="4" t="n">
-        <v>54.06</v>
+        <v>20.22</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>91.2</v>
+        <v>40.12</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>7028</v>
+        <v>5257</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>11856</v>
+        <v>10431</v>
       </c>
       <c r="V44" s="7" t="n">
-        <v>4761</v>
+        <v>5110</v>
       </c>
       <c r="W44" s="8" t="n">
-        <v>67.7</v>
+        <v>97.2</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24350 CE</t>
+          <t>NIFTY 24450 CE</t>
         </is>
       </c>
       <c r="Q45" s="9" t="inlineStr">
@@ -5154,22 +5154,22 @@
         </is>
       </c>
       <c r="R45" s="11" t="n">
-        <v>120.92</v>
+        <v>76.89</v>
       </c>
       <c r="S45" s="11" t="n">
-        <v>127.21</v>
+        <v>81.38</v>
       </c>
       <c r="T45" s="13" t="n">
-        <v>15720</v>
+        <v>9996</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>16537</v>
+        <v>10579</v>
       </c>
       <c r="V45" s="14" t="n">
-        <v>740</v>
+        <v>517</v>
       </c>
       <c r="W45" s="15" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="X45" s="9" t="n">
         <v>2</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24350 PE</t>
+          <t>NIFTY 24250 PE</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5256,28 +5256,28 @@
         </is>
       </c>
       <c r="R46" s="4" t="n">
-        <v>127.27</v>
+        <v>81.56</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>127.03</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>16545</v>
+        <v>15904</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>16514</v>
+        <v>15857</v>
       </c>
       <c r="V46" s="17" t="n">
-        <v>-109</v>
+        <v>-124</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="X46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24600 PE</t>
+          <t>NIFTY 24500 PE</t>
         </is>
       </c>
       <c r="Q47" s="9" t="inlineStr">
@@ -5358,28 +5358,28 @@
         </is>
       </c>
       <c r="R47" s="11" t="n">
-        <v>74.90000000000001</v>
+        <v>32.97</v>
       </c>
       <c r="S47" s="11" t="n">
-        <v>59.04</v>
+        <v>23.99</v>
       </c>
       <c r="T47" s="13" t="n">
-        <v>9737</v>
+        <v>6429</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>7675</v>
+        <v>4678</v>
       </c>
       <c r="V47" s="20" t="n">
-        <v>-2124</v>
+        <v>-1808</v>
       </c>
       <c r="W47" s="21" t="n">
-        <v>-21.8</v>
+        <v>-28.1</v>
       </c>
       <c r="X47" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y47" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z47" s="10" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24550 PE</t>
+          <t>NIFTY 24450 PE</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5460,28 +5460,28 @@
         </is>
       </c>
       <c r="R48" s="4" t="n">
-        <v>131.49</v>
+        <v>86.06</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>122.96</v>
+        <v>79.52</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>8547</v>
+        <v>11188</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>7992</v>
+        <v>10338</v>
       </c>
       <c r="V48" s="17" t="n">
-        <v>-617</v>
+        <v>-917</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>-7.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24650 CE</t>
+          <t>NIFTY 24750 CE</t>
         </is>
       </c>
       <c r="Q49" s="9" t="inlineStr">
@@ -5562,22 +5562,22 @@
         </is>
       </c>
       <c r="R49" s="11" t="n">
-        <v>142.48</v>
+        <v>98.08</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>123.89</v>
+        <v>83.52</v>
       </c>
       <c r="T49" s="13" t="n">
-        <v>18522</v>
+        <v>12750</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>16106</v>
+        <v>10858</v>
       </c>
       <c r="V49" s="20" t="n">
-        <v>-2495</v>
+        <v>-1961</v>
       </c>
       <c r="W49" s="21" t="n">
-        <v>-13.5</v>
+        <v>-15.4</v>
       </c>
       <c r="X49" s="9" t="n">
         <v>2</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">

--- a/trades/by_strategy/trendline_reversal.xlsx
+++ b/trades/by_strategy/trendline_reversal.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>197.51</v>
+        <v>151.21</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>237.89</v>
+        <v>185.32</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>25676</v>
+        <v>19657</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>30926</v>
+        <v>24092</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>5147</v>
+        <v>4344</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>2</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr">
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="R15" s="11" t="n">
-        <v>166.67</v>
+        <v>120.65</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>147.4</v>
+        <v>105.17</v>
       </c>
       <c r="T15" s="13" t="n">
-        <v>21667</v>
+        <v>15684</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>19162</v>
+        <v>13672</v>
       </c>
       <c r="V15" s="20" t="n">
-        <v>-2589</v>
+        <v>-2086</v>
       </c>
       <c r="W15" s="21" t="n">
-        <v>-11.9</v>
+        <v>-13.3</v>
       </c>
       <c r="X15" s="9" t="n">
         <v>2</v>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 3 (Expensive]</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23250 PE</t>
+          <t>NIFTY 23150 PE</t>
         </is>
       </c>
       <c r="Q33" s="9" t="inlineStr">
@@ -3930,22 +3930,22 @@
         </is>
       </c>
       <c r="R33" s="11" t="n">
-        <v>163.36</v>
+        <v>117.45</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>170.08</v>
+        <v>122.71</v>
       </c>
       <c r="T33" s="13" t="n">
-        <v>21237</v>
+        <v>15268</v>
       </c>
       <c r="U33" s="13" t="n">
-        <v>22110</v>
+        <v>15952</v>
       </c>
       <c r="V33" s="14" t="n">
-        <v>786</v>
+        <v>607</v>
       </c>
       <c r="W33" s="15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="X33" s="9" t="n">
         <v>2</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24600 CE</t>
+          <t>NIFTY 24700 CE</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5664,22 +5664,22 @@
         </is>
       </c>
       <c r="R50" s="4" t="n">
-        <v>160.62</v>
+        <v>115.06</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>160.27</v>
+        <v>114.72</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>20881</v>
+        <v>14958</v>
       </c>
       <c r="U50" s="6" t="n">
-        <v>20835</v>
+        <v>14914</v>
       </c>
       <c r="V50" s="17" t="n">
-        <v>-131</v>
+        <v>-119</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="X50" s="2" t="n">
         <v>2</v>

--- a/trades/by_strategy/trendline_reversal.xlsx
+++ b/trades/by_strategy/trendline_reversal.xlsx
@@ -40,13 +40,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0015803D"/>
+      <color rgb="00B91C1C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B91C1C"/>
+      <color rgb="0015803D"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -131,7 +131,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,7 +143,7 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,7 +152,7 @@
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,10 +161,10 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -538,7 +538,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -547,7 +547,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
@@ -698,12 +698,12 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -723,89 +723,89 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>22610.25</v>
+        <v>24652.45</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>22575.35</v>
+        <v>24616.6</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>22686.15</v>
+        <v>24760</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>34.9</v>
+        <v>35.85</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>22686.15</v>
+        <v>24635.65</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N2" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>-16.8</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>2.09</v>
+        <v>-0.47</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 24750 CE</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>151.21</v>
+        <v>98.08</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>185.32</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>19657</v>
+        <v>19126</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>24092</v>
+        <v>17802</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>4344</v>
+        <v>-1405</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>22.1</v>
+        <v>-7.3</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
+          <t>11:15 trendline breakout: 5m close 24,652.45 above descending line 24,638.54 (slope -0.69) | Anchored by swing highs at 10:35 (24,643.35) and 10:55 (24,640.60)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -825,89 +825,89 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.05R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G3" s="11" t="n">
-        <v>22736.1</v>
+        <v>24538.2</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>22790.35</v>
+        <v>24584.65</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>22491.97</v>
+        <v>24398.85</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>54.25</v>
+        <v>46.45</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>22678.95</v>
+        <v>24538.25</v>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N3" s="11" t="n">
-        <v>57.15</v>
+        <v>-0.05</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>1.05</v>
+        <v>-0</v>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22650 PE</t>
+          <t>NIFTY 24450 PE</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R3" s="11" t="n">
-        <v>176.29</v>
+        <v>86.06</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>201.28</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="T3" s="13" t="n">
-        <v>45835</v>
+        <v>16782</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>52333</v>
+        <v>16708</v>
       </c>
       <c r="V3" s="14" t="n">
-        <v>6356</v>
+        <v>-152</v>
       </c>
       <c r="W3" s="15" t="n">
-        <v>13.9</v>
+        <v>-0.9</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z3" s="10" t="inlineStr">
         <is>
-          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
+          <t>14:10 trendline breakdown: 5m close 24,538.20 below ascending line 24,550.02 (slope +0.78) | Anchored by swing lows at 12:15 (24,532.90) and 13:35 (24,545.35)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -917,99 +917,99 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>22781.5</v>
+        <v>24585.4</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>22744.75</v>
+        <v>24615.45</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22891.75</v>
+        <v>24525.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>36.75</v>
+        <v>30.05</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>22781.5</v>
+        <v>24593.95</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="16" t="n">
-        <v>0</v>
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>-0.28</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22900 CE</t>
+          <t>NIFTY 24500 PE</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>164.2</v>
+        <v>32.97</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>164.05</v>
+        <v>29.83</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>42692</v>
+        <v>6429</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>42653</v>
-      </c>
-      <c r="V4" s="17" t="n">
-        <v>-166</v>
-      </c>
-      <c r="W4" s="18" t="n">
-        <v>-0.4</v>
+        <v>5817</v>
+      </c>
+      <c r="V4" s="7" t="n">
+        <v>-671</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>-10.4</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:35 trendline breakdown: 5m close 24,585.40 below ascending line 24,601.97 (slope +3.94) | Anchored by swing lows at 09:35 (24,511.30) and 11:10 (24,586.20) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1033,23 +1033,23 @@
         </is>
       </c>
       <c r="G5" s="11" t="n">
-        <v>22573.4</v>
+        <v>24334.05</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>22617.45</v>
+        <v>24364.2</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>22390.45</v>
+        <v>24243.6</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>44.05</v>
+        <v>30.15</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>22573.4</v>
+        <v>24334.05</v>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -1060,36 +1060,36 @@
       <c r="N5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="19" t="n">
+      <c r="O5" s="12" t="n">
         <v>-0</v>
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 24250 PE</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>37.68</v>
+        <v>81.56</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>37.25</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>7348</v>
+        <v>15904</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>7264</v>
-      </c>
-      <c r="V5" s="20" t="n">
-        <v>-145</v>
-      </c>
-      <c r="W5" s="21" t="n">
-        <v>-2</v>
+        <v>15857</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>-124</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>-0.8</v>
       </c>
       <c r="X5" s="9" t="n">
         <v>3</v>
@@ -1099,19 +1099,19 @@
       </c>
       <c r="Z5" s="10" t="inlineStr">
         <is>
-          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>10:25 trendline breakdown: 5m close 24,334.05 below ascending line 24,340.50 (slope +3.59) | Anchored by swing lows at 09:30 (24,304.60) and 09:55 (24,322.55)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1121,99 +1121,99 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.39R)</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>23096.8</v>
+        <v>24357.35</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>23141.15</v>
+        <v>24322.35</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22917.3</v>
+        <v>24425.9</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>44.35</v>
+        <v>35</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>23141.15</v>
+        <v>24371.05</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Time (15:10)</t>
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-44.35</v>
-      </c>
-      <c r="O6" s="22" t="n">
-        <v>-1</v>
+        <v>13.7</v>
+      </c>
+      <c r="O6" s="16" t="n">
+        <v>0.39</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23000 PE</t>
+          <t>NIFTY 24450 CE</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>76.78</v>
+        <v>76.89</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>61.28</v>
+        <v>81.38</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>9981</v>
+        <v>14994</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>7966</v>
+        <v>15869</v>
       </c>
       <c r="V6" s="17" t="n">
-        <v>-2078</v>
+        <v>799</v>
       </c>
       <c r="W6" s="18" t="n">
-        <v>-20.8</v>
+        <v>5.3</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:45 trendline breakout: 5m close 24,357.35 above descending line 24,345.88 (slope -0.59) | Anchored by swing highs at 12:25 (24,354.65) and 13:15 (24,348.80)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1233,89 +1233,89 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.87R)</t>
+          <t>TARGET HIT (3R)</t>
         </is>
       </c>
       <c r="G7" s="11" t="n">
-        <v>22975.1</v>
+        <v>24285.5</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>22941.5</v>
+        <v>24251.55</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>23075.9</v>
+        <v>24354.6</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>33.6</v>
+        <v>33.95</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>23033.5</v>
+        <v>24354.6</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Partial + Structure Trail</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="N7" s="11" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>1.87</v>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="O7" s="19" t="n">
+        <v>2.02</v>
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23100 CE</t>
+          <t>NIFTY 24400 CE</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R7" s="11" t="n">
-        <v>89.03</v>
+        <v>20.22</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>111.19</v>
+        <v>40.12</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>11574</v>
+        <v>5257</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>14455</v>
-      </c>
-      <c r="V7" s="14" t="n">
-        <v>2808</v>
-      </c>
-      <c r="W7" s="15" t="n">
-        <v>24.3</v>
+        <v>10431</v>
+      </c>
+      <c r="V7" s="20" t="n">
+        <v>5110</v>
+      </c>
+      <c r="W7" s="21" t="n">
+        <v>97.2</v>
       </c>
       <c r="X7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z7" s="10" t="inlineStr">
         <is>
-          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:20 trendline breakout: 5m close 24,285.50 above descending line 24,271.71 (slope -1.31) | Anchored by swing highs at 09:40 (24,312.45) and 12:00 (24,275.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1339,85 +1339,85 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>22744.6</v>
+        <v>24177.3</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>22707.85</v>
+        <v>24123.95</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22854.85</v>
+        <v>24309.85</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>36.75</v>
+        <v>53.35</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>22707.85</v>
+        <v>24181.85</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-36.75</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <v>-1</v>
+        <v>4.55</v>
+      </c>
+      <c r="O8" s="16" t="n">
+        <v>0.09</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22850 CE</t>
+          <t>NIFTY 24300 CE</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>106.13</v>
+        <v>101.43</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>92.19</v>
+        <v>102.92</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>13797</v>
+        <v>26372</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>11985</v>
+        <v>26759</v>
       </c>
       <c r="V8" s="17" t="n">
-        <v>-1882</v>
+        <v>291</v>
       </c>
       <c r="W8" s="18" t="n">
-        <v>-13.6</v>
+        <v>1.1</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>11:00 trendline breakout: 5m close 22,744.60 above descending line 22,738.33 (slope -1.39) | Anchored by swing highs at 09:45 (22,757.80) and 10:40 (22,742.50)</t>
+          <t>13:55 trendline breakout: 5m close 24,177.30 above descending line 24,137.15 (slope -2.30) | Anchored by swing highs at 11:55 (24,189.95) and 12:55 (24,162.40)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1437,89 +1437,89 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.32R)</t>
         </is>
       </c>
       <c r="G9" s="11" t="n">
-        <v>22557.5</v>
+        <v>24174.25</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>22525.3</v>
+        <v>24136.7</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>22647.55</v>
+        <v>24293.9</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>32.2</v>
+        <v>37.55</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>22525.3</v>
+        <v>24186.3</v>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 35m)</t>
         </is>
       </c>
       <c r="N9" s="11" t="n">
-        <v>-32.2</v>
-      </c>
-      <c r="O9" s="23" t="n">
-        <v>-1</v>
+        <v>12.05</v>
+      </c>
+      <c r="O9" s="19" t="n">
+        <v>0.32</v>
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22650 CE</t>
+          <t>NIFTY 24250 CE</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R9" s="11" t="n">
-        <v>135.25</v>
+        <v>86.78</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>122.03</v>
+        <v>91.42</v>
       </c>
       <c r="T9" s="13" t="n">
-        <v>35165</v>
+        <v>16922</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>31728</v>
+        <v>17827</v>
       </c>
       <c r="V9" s="20" t="n">
-        <v>-3545</v>
+        <v>825</v>
       </c>
       <c r="W9" s="21" t="n">
-        <v>-10.1</v>
+        <v>4.9</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z9" s="10" t="inlineStr">
         <is>
-          <t>13:15 trendline breakout: 5m close 22,557.50 above descending line 22,550.30 (slope -0.95) | Anchored by swing highs at 12:30 (22,557.90) and 12:50 (22,554.10)</t>
+          <t>12:40 trendline breakout: 5m close 24,174.25 above descending line 24,159.12 (slope -0.53) | Anchored by swing highs at 11:05 (24,168.75) and 11:55 (24,163.40) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1539,89 +1539,89 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.07R)</t>
+          <t>TRAILED (+1.21R)</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>22363</v>
+        <v>24093.5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>22413.65</v>
+        <v>24123.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>22211.05</v>
+        <v>24028.55</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>50.65</v>
+        <v>30.2</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>22308.65</v>
+        <v>24056.9</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>54.35</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>1.07</v>
+        <v>36.6</v>
+      </c>
+      <c r="O10" s="16" t="n">
+        <v>1.21</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22250 PE</t>
+          <t>NIFTY 24000 PE</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>27.58</v>
+        <v>107.67</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>42.06</v>
+        <v>122.74</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>5378</v>
+        <v>27994</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>8202</v>
-      </c>
-      <c r="V10" s="7" t="n">
-        <v>2762</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>51.4</v>
+        <v>31912</v>
+      </c>
+      <c r="V10" s="17" t="n">
+        <v>3813</v>
+      </c>
+      <c r="W10" s="18" t="n">
+        <v>13.6</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>13:15 trendline breakdown: 5m close 22,363.00 below ascending line 22,374.22 (slope +1.81) | Anchored by swing lows at 12:10 (22,352.55) and 12:50 (22,367.00)</t>
+          <t>12:55 trendline breakdown: 5m close 24,093.50 below ascending line 24,103.23 (slope +1.72) | Anchored by swing lows at 10:40 (24,058.60) and 12:25 (24,094.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1641,89 +1641,89 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.71R)</t>
+          <t>TRAILED (+0.50R)</t>
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>22526.15</v>
+        <v>23838.35</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>22490.25</v>
+        <v>23796.1</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>22596.05</v>
+        <v>23949.6</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>35.9</v>
+        <v>42.25</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>22551.65</v>
+        <v>23859.3</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N11" s="11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O11" s="12" t="n">
-        <v>0.71</v>
+        <v>20.95</v>
+      </c>
+      <c r="O11" s="19" t="n">
+        <v>0.5</v>
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22650 CE</t>
+          <t>NIFTY 23950 CE</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R11" s="11" t="n">
-        <v>91.84</v>
+        <v>93.11</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>101.07</v>
+        <v>101.02</v>
       </c>
       <c r="T11" s="13" t="n">
-        <v>11939</v>
+        <v>18156</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>13139</v>
-      </c>
-      <c r="V11" s="14" t="n">
-        <v>1129</v>
-      </c>
-      <c r="W11" s="15" t="n">
-        <v>9.5</v>
+        <v>19699</v>
+      </c>
+      <c r="V11" s="20" t="n">
+        <v>1459</v>
+      </c>
+      <c r="W11" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z11" s="10" t="inlineStr">
         <is>
-          <t>13:45 trendline breakout: 5m close 22,526.15 above descending line 22,509.90 (slope -0.60) | Anchored by swing highs at 12:55 (22,515.30) and 13:20 (22,512.30)</t>
+          <t>12:15 trendline breakout: 5m close 23,838.35 above descending line 23,820.60 (slope -3.18) | Anchored by swing highs at 10:50 (23,871.55) and 11:55 (23,830.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1743,89 +1743,89 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+0.45R)</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>22486.7</v>
+        <v>23959.1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>22522.6</v>
+        <v>23996.75</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>22325.15</v>
+        <v>23876.45</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>35.9</v>
+        <v>37.65</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>22486.7</v>
+        <v>23942.3</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>-0</v>
+        <v>0.45</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22400 PE</t>
+          <t>NIFTY 23850 PE</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>106.72</v>
+        <v>68.78</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>106.42</v>
+        <v>74.53</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>13874</v>
+        <v>13412</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>13835</v>
+        <v>14533</v>
       </c>
       <c r="V12" s="17" t="n">
-        <v>-112</v>
+        <v>1048</v>
       </c>
       <c r="W12" s="18" t="n">
-        <v>-0.8</v>
+        <v>7.8</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>11:45 trendline breakdown: 5m close 22,486.70 below ascending line 22,489.01 (slope +1.26) | Anchored by swing lows at 10:35 (22,472.65) and 11:05 (22,480.20) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:05 trendline breakdown: 5m close 23,959.10 below ascending line 23,974.68 (slope +1.53) | Anchored by swing lows at 10:45 (23,951.80) and 11:15 (23,960.95) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1845,89 +1845,89 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G13" s="11" t="n">
-        <v>22460.8</v>
+        <v>23670.35</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>22503.1</v>
+        <v>23703.6</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>22333.9</v>
+        <v>23570.6</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>42.3</v>
+        <v>33.25</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>22333.9</v>
+        <v>23667.55</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N13" s="11" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="O13" s="12" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
+      </c>
+      <c r="O13" s="19" t="n">
+        <v>0.08</v>
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22350 PE</t>
+          <t>NIFTY 23550 PE</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R13" s="11" t="n">
-        <v>99.54000000000001</v>
+        <v>95.08</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>155.48</v>
+        <v>95.88</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>12940</v>
+        <v>24721</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>20212</v>
-      </c>
-      <c r="V13" s="14" t="n">
-        <v>7191</v>
-      </c>
-      <c r="W13" s="15" t="n">
-        <v>55.6</v>
+        <v>24929</v>
+      </c>
+      <c r="V13" s="20" t="n">
+        <v>115</v>
+      </c>
+      <c r="W13" s="21" t="n">
+        <v>0.5</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z13" s="10" t="inlineStr">
         <is>
-          <t>10:20 trendline breakdown: 5m close 22,460.80 below ascending line 22,467.75 (slope +3.68) | Anchored by swing lows at 09:45 (22,445.70) and 10:05 (22,460.40)</t>
+          <t>11:00 trendline breakdown: 5m close 23,670.35 below ascending line 23,672.27 (slope +1.51) | Anchored by swing lows at 10:05 (23,657.20) and 10:40 (23,667.75)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1947,89 +1947,89 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>22674.9</v>
+        <v>23502.35</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>22722.25</v>
+        <v>23537.35</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>22588.4</v>
+        <v>23397.35</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>47.35</v>
+        <v>35</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>22588.4</v>
+        <v>23510.75</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>86.5</v>
+        <v>-8.4</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>1.91</v>
+        <v>-0.24</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 23400 PE</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>104.46</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>139.92</v>
+        <v>87.86</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>13580</v>
+        <v>17796</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>18190</v>
+        <v>17133</v>
       </c>
       <c r="V14" s="7" t="n">
-        <v>4531</v>
+        <v>-742</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>33.4</v>
+        <v>-4.2</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>12:15 trendline breakdown: 5m close 22,674.90 below ascending line 22,683.45 (slope +3.05) | Anchored by swing lows at 11:30 (22,659.05) and 11:45 (22,668.20) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:55 trendline breakdown: 5m close 23,502.35 below ascending line 23,518.71 (slope +1.22) | Anchored by swing lows at 10:40 (23,501.60) and 11:25 (23,512.60) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2049,89 +2049,89 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>FLAT</t>
         </is>
       </c>
       <c r="G15" s="11" t="n">
-        <v>22713.3</v>
+        <v>23431.8</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>22674.75</v>
+        <v>23400.35</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>22828.95</v>
+        <v>23486.7</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>38.55</v>
+        <v>31.45</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>22674.75</v>
+        <v>23431.8</v>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Breakeven</t>
         </is>
       </c>
       <c r="N15" s="11" t="n">
-        <v>-38.55</v>
-      </c>
-      <c r="O15" s="23" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 23550 CE</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R15" s="11" t="n">
-        <v>120.65</v>
+        <v>81.92</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>105.17</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="T15" s="13" t="n">
-        <v>15684</v>
+        <v>15974</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>13672</v>
-      </c>
-      <c r="V15" s="20" t="n">
-        <v>-2086</v>
-      </c>
-      <c r="W15" s="21" t="n">
-        <v>-13.3</v>
+        <v>15842</v>
+      </c>
+      <c r="V15" s="14" t="n">
+        <v>-209</v>
+      </c>
+      <c r="W15" s="15" t="n">
+        <v>-1.3</v>
       </c>
       <c r="X15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z15" s="10" t="inlineStr">
         <is>
-          <t>12:05 trendline breakout: 5m close 22,713.30 above descending line 22,685.03 (slope -2.33) | Anchored by swing highs at 11:05 (22,710.70) and 11:35 (22,696.70) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:50 trendline breakout: 5m close 23,431.80 above descending line 23,431.30 (slope -2.58) | Anchored by swing highs at 11:15 (23,446.80) and 11:30 (23,439.05) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2151,89 +2151,89 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+0.29R)</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>22689.75</v>
+        <v>23437.8</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>22728.7</v>
+        <v>23470.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>22564.8</v>
+        <v>23340.6</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>38.95</v>
+        <v>32.4</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>22709.55</v>
+        <v>23428.5</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="O16" s="22" t="n">
-        <v>-0.51</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O16" s="16" t="n">
+        <v>0.29</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22600 PE</t>
+          <t>NIFTY 23350 PE</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R16" s="4" t="n">
-        <v>144.03</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>135.53</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>37448</v>
+        <v>17997</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>35238</v>
+        <v>18658</v>
       </c>
       <c r="V16" s="17" t="n">
-        <v>-2324</v>
+        <v>579</v>
       </c>
       <c r="W16" s="18" t="n">
-        <v>-6.2</v>
+        <v>3.2</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>14:30 trendline breakdown: 5m close 22,689.75 below ascending line 22,712.70 (slope +1.79) | Anchored by swing lows at 13:25 (22,691.25) and 13:45 (22,698.40)</t>
+          <t>13:00 trendline breakdown: 5m close 23,437.80 below ascending line 23,452.19 (slope +3.12) | Anchored by swing lows at 11:40 (23,405.35) and 12:35 (23,439.70) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2243,33 +2243,33 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.13R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G17" s="11" t="n">
-        <v>22670.3</v>
+        <v>23326.7</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>22636.25</v>
+        <v>23358.9</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>22772.45</v>
+        <v>23235.25</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>34.05</v>
+        <v>32.2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>22708.8</v>
+        <v>23328.9</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
@@ -2278,42 +2278,42 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N17" s="11" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>1.13</v>
+        <v>-2.2</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22750 CE</t>
+          <t>NIFTY 23250 PE</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R17" s="11" t="n">
-        <v>150.92</v>
+        <v>124.18</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>167.14</v>
+        <v>122.99</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>39239</v>
+        <v>32287</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>43456</v>
+        <v>31977</v>
       </c>
       <c r="V17" s="14" t="n">
-        <v>4091</v>
+        <v>-416</v>
       </c>
       <c r="W17" s="15" t="n">
-        <v>10.4</v>
+        <v>-1.3</v>
       </c>
       <c r="X17" s="9" t="n">
         <v>4</v>
@@ -2323,19 +2323,19 @@
       </c>
       <c r="Z17" s="10" t="inlineStr">
         <is>
-          <t>10:40 trendline breakout: 5m close 22,670.30 above descending line 22,660.45 (slope -0.86) | Anchored by swing highs at 09:55 (22,667.35) and 10:15 (22,663.90)</t>
+          <t>12:20 trendline breakdown: 5m close 23,326.70 below ascending line 23,329.24 (slope +1.94) | Anchored by swing lows at 11:30 (23,311.80) and 11:50 (23,319.55) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2345,94 +2345,94 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.30R)</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>22558.75</v>
+        <v>23245</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>22524.7</v>
+        <v>23283.15</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>22711.97</v>
+        <v>23123.95</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>34.05</v>
+        <v>38.15</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>22524.7</v>
+        <v>23233.6</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 35m)</t>
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-34.05</v>
-      </c>
-      <c r="O18" s="22" t="n">
-        <v>-1</v>
+        <v>11.4</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <v>0.3</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22650 CE</t>
+          <t>NIFTY 23150 PE</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>103.57</v>
+        <v>117.45</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>90.12</v>
+        <v>121.75</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>13464</v>
+        <v>22903</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>11716</v>
+        <v>23741</v>
       </c>
       <c r="V18" s="17" t="n">
-        <v>-1818</v>
+        <v>748</v>
       </c>
       <c r="W18" s="18" t="n">
-        <v>-13.5</v>
+        <v>3.3</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>11:40 trendline breakout: 5m close 22,558.75 above descending line 22,551.28 (slope -3.59) | Anchored by swing highs at 10:35 (22,594.40) and 11:15 (22,565.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:25 trendline breakdown: 5m close 23,245.00 below ascending line 23,252.00 (slope +2.86) | Anchored by swing lows at 12:00 (23,206.20) and 13:00 (23,240.55)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2457,89 +2457,89 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G19" s="11" t="n">
-        <v>22547.75</v>
+        <v>23238.4</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>22586.45</v>
+        <v>23288.9</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>22431.65</v>
+        <v>23119.35</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>38.7</v>
+        <v>50.5</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>22431.65</v>
+        <v>23252.3</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N19" s="11" t="n">
-        <v>116.1</v>
-      </c>
-      <c r="O19" s="12" t="n">
-        <v>2.5</v>
+        <v>-13.9</v>
+      </c>
+      <c r="O19" s="22" t="n">
+        <v>-0.28</v>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 23150 PE</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R19" s="11" t="n">
-        <v>100.66</v>
+        <v>105.29</v>
       </c>
       <c r="S19" s="11" t="n">
-        <v>152.27</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>13086</v>
+        <v>20532</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>19795</v>
+        <v>19401</v>
       </c>
       <c r="V19" s="14" t="n">
-        <v>6628</v>
+        <v>-1215</v>
       </c>
       <c r="W19" s="15" t="n">
-        <v>50.6</v>
+        <v>-5.9</v>
       </c>
       <c r="X19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y19" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z19" s="10" t="inlineStr">
         <is>
-          <t>11:05 trendline breakdown: 5m close 22,547.75 below ascending line 22,551.58 (slope +1.23) | Anchored by swing lows at 10:25 (22,543.00) and 10:45 (22,547.90)</t>
+          <t>11:05 trendline breakdown: 5m close 23,238.40 below ascending line 23,267.79 (slope +2.40) | Anchored by swing lows at 09:40 (23,229.45) and 10:45 (23,260.60)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2549,99 +2549,99 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.74R)</t>
+          <t>TRAILED (+1.29R)</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>22708.45</v>
+        <v>23276.15</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>22746.65</v>
+        <v>23229.65</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>22572.65</v>
+        <v>23415.65</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>38.2</v>
+        <v>46.5</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>22651.95</v>
+        <v>23336.3</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Partial + Structure Trail</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>1.74</v>
+        <v>60.15</v>
+      </c>
+      <c r="O20" s="16" t="n">
+        <v>1.29</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22600 PE</t>
+          <t>NIFTY 23400 CE</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R20" s="4" t="n">
-        <v>107.79</v>
+        <v>92.11</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>130.95</v>
+        <v>115.65</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>14013</v>
+        <v>17961</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>17024</v>
-      </c>
-      <c r="V20" s="7" t="n">
-        <v>2933</v>
-      </c>
-      <c r="W20" s="8" t="n">
-        <v>20.9</v>
+        <v>22552</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>4503</v>
+      </c>
+      <c r="W20" s="18" t="n">
+        <v>25.1</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>14:15 trendline breakdown: 5m close 22,708.45 below ascending line 22,722.98 (slope +1.63) | Anchored by swing lows at 11:15 (22,666.05) and 13:45 (22,714.85)</t>
+          <t>11:45 trendline breakout: 5m close 23,276.15 above descending line 23,251.16 (slope -3.64) | Anchored by swing highs at 10:35 (23,298.45) and 10:55 (23,283.90) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2651,99 +2651,99 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.10R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G21" s="11" t="n">
-        <v>22737</v>
+        <v>23306.8</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>22699.5</v>
+        <v>23337</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>22849.5</v>
+        <v>23198.05</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>37.5</v>
+        <v>30.2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>22778.45</v>
+        <v>23309.25</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N21" s="11" t="n">
-        <v>41.45</v>
-      </c>
-      <c r="O21" s="12" t="n">
-        <v>1.1</v>
+        <v>-2.45</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>-0.08</v>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22850 CE</t>
+          <t>NIFTY 23200 PE</t>
         </is>
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R21" s="11" t="n">
-        <v>108.11</v>
+        <v>76.41</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>124.5</v>
+        <v>75.19</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>14054</v>
+        <v>14900</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>16185</v>
+        <v>14662</v>
       </c>
       <c r="V21" s="14" t="n">
-        <v>2054</v>
+        <v>-312</v>
       </c>
       <c r="W21" s="15" t="n">
-        <v>14.6</v>
+        <v>-2.1</v>
       </c>
       <c r="X21" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z21" s="10" t="inlineStr">
         <is>
-          <t>12:00 trendline breakout: 5m close 22,737.00 above descending line 22,716.67 (slope -1.21) | Anchored by swing highs at 11:00 (22,729.95) and 11:35 (22,721.50) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>10:25 trendline breakdown: 5m close 23,306.80 below ascending line 23,320.10 (slope +3.70) | Anchored by swing lows at 09:35 (23,286.80) and 10:05 (23,309.00)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2763,89 +2763,89 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>TRAILED (+0.65R)</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>22613</v>
+        <v>23331.65</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>22575.55</v>
+        <v>23299.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>22749.45</v>
+        <v>23427.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>37.45</v>
+        <v>31.95</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>22749.45</v>
+        <v>23352.25</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>136.45</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>2.82</v>
+        <v>20.6</v>
+      </c>
+      <c r="O22" s="16" t="n">
+        <v>0.65</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 23450 CE</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>133.1</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>198.78</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>34606</v>
+        <v>13837</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>51683</v>
-      </c>
-      <c r="V22" s="7" t="n">
-        <v>16941</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>49</v>
+        <v>15163</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>1251</v>
+      </c>
+      <c r="W22" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>10:45 trendline breakout: 5m close 22,613.00 above descending line 22,598.32 (slope -2.33) | Anchored by swing highs at 09:55 (22,619.25) and 10:25 (22,605.30)</t>
+          <t>13:55 trendline breakout: 5m close 23,331.65 above descending line 23,328.47 (slope -1.41) | Anchored by swing highs at 13:00 (23,342.55) and 13:30 (23,334.10)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2855,99 +2855,99 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.42R)</t>
         </is>
       </c>
       <c r="G23" s="11" t="n">
-        <v>23056.75</v>
+        <v>23423.8</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>23094.85</v>
+        <v>23392.65</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>22942.45</v>
+        <v>23517.25</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>38.1</v>
+        <v>31.15</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>23094.85</v>
+        <v>23436.85</v>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N23" s="11" t="n">
-        <v>-38.1</v>
-      </c>
-      <c r="O23" s="23" t="n">
-        <v>-1</v>
+        <v>13.05</v>
+      </c>
+      <c r="O23" s="19" t="n">
+        <v>0.42</v>
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22950 PE</t>
+          <t>NIFTY 23500 CE</t>
         </is>
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R23" s="11" t="n">
-        <v>77.53</v>
+        <v>27.92</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>63.82</v>
+        <v>31.47</v>
       </c>
       <c r="T23" s="13" t="n">
-        <v>10079</v>
+        <v>5444</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>8297</v>
+        <v>6137</v>
       </c>
       <c r="V23" s="20" t="n">
-        <v>-1846</v>
+        <v>634</v>
       </c>
       <c r="W23" s="21" t="n">
-        <v>-18.3</v>
+        <v>11.6</v>
       </c>
       <c r="X23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y23" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z23" s="10" t="inlineStr">
         <is>
-          <t>12:45 trendline breakdown: 5m close 23,056.75 below ascending line 23,065.90 (slope +0.80) | Anchored by swing lows at 10:45 (23,047.50) and 12:00 (23,059.50) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:20 trendline breakout: 5m close 23,423.80 above descending line 23,413.00 (slope -1.25) | Anchored by swing highs at 12:30 (23,424.25) and 12:55 (23,418.00)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2967,43 +2967,43 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>FLAT</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>23207.5</v>
+        <v>23328.75</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>23249.7</v>
+        <v>23360.35</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>23080.9</v>
+        <v>23233.95</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>42.2</v>
+        <v>31.6</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>23080.9</v>
+        <v>23328.75</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Breakeven</t>
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>126.6</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>2.5</v>
+        <v>0</v>
+      </c>
+      <c r="O24" s="23" t="n">
+        <v>-0</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23100 PE</t>
+          <t>NIFTY 23250 PE</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3012,44 +3012,44 @@
         </is>
       </c>
       <c r="R24" s="4" t="n">
-        <v>67.95</v>
+        <v>109.47</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>122.17</v>
+        <v>109.3</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>8834</v>
+        <v>28462</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>15882</v>
+        <v>28418</v>
       </c>
       <c r="V24" s="7" t="n">
-        <v>6975</v>
+        <v>-144</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>79</v>
+        <v>-0.5</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>11:35 trendline breakdown: 5m close 23,207.50 below ascending line 23,218.01 (slope +1.54) | Anchored by swing lows at 10:20 (23,196.45) and 11:10 (23,211.85) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:50 trendline breakdown: 5m close 23,328.75 below ascending line 23,333.89 (slope +1.64) | Anchored by swing lows at 13:00 (23,319.15) and 13:20 (23,325.70)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -3069,43 +3069,43 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+1.41R)</t>
         </is>
       </c>
       <c r="G25" s="11" t="n">
-        <v>23237.05</v>
+        <v>23393.35</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>23206</v>
+        <v>23350.6</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>23346.7</v>
+        <v>23486</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>31.05</v>
+        <v>42.75</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>23206</v>
+        <v>23453.75</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N25" s="11" t="n">
-        <v>-31.05</v>
-      </c>
-      <c r="O25" s="23" t="n">
-        <v>-1</v>
+        <v>60.4</v>
+      </c>
+      <c r="O25" s="19" t="n">
+        <v>1.41</v>
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23350 CE</t>
+          <t>NIFTY 23500 CE</t>
         </is>
       </c>
       <c r="Q25" s="9" t="inlineStr">
@@ -3114,22 +3114,22 @@
         </is>
       </c>
       <c r="R25" s="11" t="n">
-        <v>66.95999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>56.45</v>
+        <v>111.64</v>
       </c>
       <c r="T25" s="13" t="n">
-        <v>13057</v>
+        <v>17088</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>11008</v>
+        <v>21770</v>
       </c>
       <c r="V25" s="20" t="n">
-        <v>-2118</v>
+        <v>4596</v>
       </c>
       <c r="W25" s="21" t="n">
-        <v>-16.2</v>
+        <v>26.9</v>
       </c>
       <c r="X25" s="9" t="n">
         <v>3</v>
@@ -3139,19 +3139,19 @@
       </c>
       <c r="Z25" s="10" t="inlineStr">
         <is>
-          <t>10:55 trendline breakout: 5m close 23,237.05 above descending line 23,231.45 (slope -1.52) | Anchored by swing highs at 10:05 (23,245.10) and 10:35 (23,236.00)</t>
+          <t>10:20 trendline breakout: 5m close 23,393.35 above descending line 23,379.20 (slope -1.60) | Anchored by swing highs at 09:45 (23,388.80) and 10:00 (23,384.00)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3171,43 +3171,43 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.41R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>23393.35</v>
+        <v>23237.05</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>23350.6</v>
+        <v>23206</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>23486</v>
+        <v>23346.7</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>42.75</v>
+        <v>31.05</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>23453.75</v>
+        <v>23223.05</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N26" s="4" t="n">
-        <v>60.4</v>
+        <v>-14</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>1.41</v>
+        <v>-0.45</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23500 CE</t>
+          <t>NIFTY 23350 CE</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3216,44 +3216,44 @@
         </is>
       </c>
       <c r="R26" s="4" t="n">
-        <v>87.63</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>111.64</v>
+        <v>61.95</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>11392</v>
+        <v>13057</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>14513</v>
+        <v>12080</v>
       </c>
       <c r="V26" s="7" t="n">
-        <v>3049</v>
+        <v>-1047</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>26.8</v>
+        <v>-8</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>10:20 trendline breakout: 5m close 23,393.35 above descending line 23,379.20 (slope -1.60) | Anchored by swing highs at 09:45 (23,388.80) and 10:00 (23,384.00)</t>
+          <t>10:55 trendline breakout: 5m close 23,237.05 above descending line 23,231.45 (slope -1.52) | Anchored by swing highs at 10:05 (23,245.10) and 10:35 (23,236.00)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -3273,43 +3273,43 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G27" s="11" t="n">
-        <v>23328.75</v>
+        <v>23207.5</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>23360.35</v>
+        <v>23249.7</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>23233.95</v>
+        <v>23080.9</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>31.6</v>
+        <v>42.2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>23328.75</v>
+        <v>23205.85</v>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N27" s="11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>-0</v>
+        <v>0.04</v>
       </c>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23250 PE</t>
+          <t>NIFTY 23100 PE</t>
         </is>
       </c>
       <c r="Q27" s="9" t="inlineStr">
@@ -3318,44 +3318,44 @@
         </is>
       </c>
       <c r="R27" s="11" t="n">
-        <v>109.47</v>
+        <v>67.95</v>
       </c>
       <c r="S27" s="11" t="n">
-        <v>109.3</v>
+        <v>68.28</v>
       </c>
       <c r="T27" s="13" t="n">
-        <v>28462</v>
+        <v>13250</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>28418</v>
-      </c>
-      <c r="V27" s="20" t="n">
-        <v>-144</v>
-      </c>
-      <c r="W27" s="21" t="n">
-        <v>-0.5</v>
+        <v>13315</v>
+      </c>
+      <c r="V27" s="14" t="n">
+        <v>-8</v>
+      </c>
+      <c r="W27" s="15" t="n">
+        <v>-0.1</v>
       </c>
       <c r="X27" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z27" s="10" t="inlineStr">
         <is>
-          <t>13:50 trendline breakdown: 5m close 23,328.75 below ascending line 23,333.89 (slope +1.64) | Anchored by swing lows at 13:00 (23,319.15) and 13:20 (23,325.70)</t>
+          <t>11:35 trendline breakdown: 5m close 23,207.50 below ascending line 23,218.01 (slope +1.54) | Anchored by swing lows at 10:20 (23,196.45) and 11:10 (23,211.85) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3365,77 +3365,77 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.45R)</t>
+          <t>TRAILED (+0.43R)</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>23423.8</v>
+        <v>23056.75</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>23392.65</v>
+        <v>23094.85</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>23517.25</v>
+        <v>22942.45</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>31.15</v>
+        <v>38.1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>23437.65</v>
+        <v>23040.45</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 40m)</t>
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v>0.45</v>
+        <v>16.3</v>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>0.43</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23500 CE</t>
+          <t>NIFTY 22950 PE</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="R28" s="4" t="n">
-        <v>27.92</v>
+        <v>77.53</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>30.45</v>
+        <v>83.16</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>5444</v>
+        <v>15118</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>5938</v>
-      </c>
-      <c r="V28" s="7" t="n">
-        <v>435</v>
-      </c>
-      <c r="W28" s="8" t="n">
-        <v>8</v>
+        <v>16216</v>
+      </c>
+      <c r="V28" s="17" t="n">
+        <v>1021</v>
+      </c>
+      <c r="W28" s="18" t="n">
+        <v>6.8</v>
       </c>
       <c r="X28" s="2" t="n">
         <v>3</v>
@@ -3445,19 +3445,19 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>13:20 trendline breakout: 5m close 23,423.80 above descending line 23,413.00 (slope -1.25) | Anchored by swing highs at 12:30 (23,424.25) and 12:55 (23,418.00)</t>
+          <t>12:45 trendline breakdown: 5m close 23,056.75 below ascending line 23,065.90 (slope +0.80) | Anchored by swing lows at 10:45 (23,047.50) and 12:00 (23,059.50) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -3477,89 +3477,89 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.65R)</t>
+          <t>TARGET HIT (3R)</t>
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>23331.65</v>
+        <v>22613</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>23299.7</v>
+        <v>22575.55</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>23427.5</v>
+        <v>22749.45</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>31.95</v>
+        <v>37.45</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>23352.25</v>
+        <v>22749.45</v>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="N29" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>0.65</v>
+        <v>136.45</v>
+      </c>
+      <c r="O29" s="19" t="n">
+        <v>2.82</v>
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23450 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="R29" s="11" t="n">
-        <v>70.95999999999999</v>
+        <v>133.1</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>77.76000000000001</v>
+        <v>198.78</v>
       </c>
       <c r="T29" s="13" t="n">
-        <v>13837</v>
+        <v>34606</v>
       </c>
       <c r="U29" s="13" t="n">
-        <v>15163</v>
-      </c>
-      <c r="V29" s="14" t="n">
-        <v>1251</v>
-      </c>
-      <c r="W29" s="15" t="n">
-        <v>9</v>
+        <v>51683</v>
+      </c>
+      <c r="V29" s="20" t="n">
+        <v>16941</v>
+      </c>
+      <c r="W29" s="21" t="n">
+        <v>49</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z29" s="10" t="inlineStr">
         <is>
-          <t>13:55 trendline breakout: 5m close 23,331.65 above descending line 23,328.47 (slope -1.41) | Anchored by swing highs at 13:00 (23,342.55) and 13:30 (23,334.10)</t>
+          <t>10:45 trendline breakout: 5m close 22,613.00 above descending line 22,598.32 (slope -2.33) | Anchored by swing highs at 09:55 (22,619.25) and 10:25 (22,605.30)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3569,77 +3569,77 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+1.10R)</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>23306.8</v>
+        <v>22737</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>23337</v>
+        <v>22699.5</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23198.05</v>
+        <v>22849.5</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>30.2</v>
+        <v>37.5</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>23337</v>
+        <v>22778.45</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-30.2</v>
-      </c>
-      <c r="O30" s="22" t="n">
-        <v>-1</v>
+        <v>41.45</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>1.1</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23200 PE</t>
+          <t>NIFTY 22850 CE</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="R30" s="4" t="n">
-        <v>76.41</v>
+        <v>108.11</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>64.75</v>
+        <v>124.5</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>14900</v>
+        <v>21081</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>12626</v>
+        <v>24278</v>
       </c>
       <c r="V30" s="17" t="n">
-        <v>-2345</v>
+        <v>3105</v>
       </c>
       <c r="W30" s="18" t="n">
-        <v>-15.7</v>
+        <v>14.7</v>
       </c>
       <c r="X30" s="2" t="n">
         <v>3</v>
@@ -3649,19 +3649,19 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>10:25 trendline breakdown: 5m close 23,306.80 below ascending line 23,320.10 (slope +3.70) | Anchored by swing lows at 09:35 (23,286.80) and 10:05 (23,309.00)</t>
+          <t>12:00 trendline breakout: 5m close 22,737.00 above descending line 22,716.67 (slope -1.21) | Anchored by swing highs at 11:00 (22,729.95) and 11:35 (22,721.50) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3671,94 +3671,94 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.29R)</t>
+          <t>TRAILED (+1.74R)</t>
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>23276.15</v>
+        <v>22708.45</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>23229.65</v>
+        <v>22746.65</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>23415.65</v>
+        <v>22572.65</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>46.5</v>
+        <v>38.2</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>23336.3</v>
+        <v>22651.95</v>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Partial + Structure Trail</t>
         </is>
       </c>
       <c r="N31" s="11" t="n">
-        <v>60.15</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>1.29</v>
+        <v>56.5</v>
+      </c>
+      <c r="O31" s="19" t="n">
+        <v>1.74</v>
       </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23400 CE</t>
+          <t>NIFTY 22600 PE</t>
         </is>
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="R31" s="11" t="n">
-        <v>92.11</v>
+        <v>107.79</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>115.65</v>
+        <v>130.95</v>
       </c>
       <c r="T31" s="13" t="n">
-        <v>11974</v>
+        <v>21019</v>
       </c>
       <c r="U31" s="13" t="n">
-        <v>15034</v>
-      </c>
-      <c r="V31" s="14" t="n">
-        <v>2986</v>
-      </c>
-      <c r="W31" s="15" t="n">
-        <v>24.9</v>
+        <v>25535</v>
+      </c>
+      <c r="V31" s="20" t="n">
+        <v>4424</v>
+      </c>
+      <c r="W31" s="21" t="n">
+        <v>21</v>
       </c>
       <c r="X31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y31" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z31" s="10" t="inlineStr">
         <is>
-          <t>11:45 trendline breakout: 5m close 23,276.15 above descending line 23,251.16 (slope -3.64) | Anchored by swing highs at 10:35 (23,298.45) and 10:55 (23,283.90) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>14:15 trendline breakdown: 5m close 22,708.45 below ascending line 22,722.98 (slope +1.63) | Anchored by swing lows at 11:15 (22,666.05) and 13:45 (22,714.85)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3787,85 +3787,85 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>23238.4</v>
+        <v>22547.75</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>23288.9</v>
+        <v>22586.45</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>23119.35</v>
+        <v>22431.65</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>50.5</v>
+        <v>38.7</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>23288.9</v>
+        <v>22558.75</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-50.5</v>
-      </c>
-      <c r="O32" s="22" t="n">
-        <v>-1</v>
+        <v>-11</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>-0.28</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23150 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="R32" s="4" t="n">
-        <v>105.29</v>
+        <v>100.66</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>85.92</v>
+        <v>96.11</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>13688</v>
+        <v>19629</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>11170</v>
-      </c>
-      <c r="V32" s="17" t="n">
-        <v>-2587</v>
-      </c>
-      <c r="W32" s="18" t="n">
-        <v>-18.9</v>
+        <v>18741</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <v>-970</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>-4.9</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>11:05 trendline breakdown: 5m close 23,238.40 below ascending line 23,267.79 (slope +2.40) | Anchored by swing lows at 09:40 (23,229.45) and 10:45 (23,260.60)</t>
+          <t>11:05 trendline breakdown: 5m close 22,547.75 below ascending line 22,551.58 (slope +1.23) | Anchored by swing lows at 10:25 (22,543.00) and 10:45 (22,547.90)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3875,99 +3875,99 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.40R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G33" s="11" t="n">
-        <v>23245</v>
+        <v>22558.75</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>23283.15</v>
+        <v>22524.7</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>23123.95</v>
+        <v>22711.97</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>38.15</v>
+        <v>34.05</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>23229.9</v>
+        <v>22524.7</v>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N33" s="11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <v>0.4</v>
+        <v>-34.05</v>
+      </c>
+      <c r="O33" s="22" t="n">
+        <v>-1</v>
       </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23150 PE</t>
+          <t>NIFTY 22650 CE</t>
         </is>
       </c>
       <c r="Q33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="R33" s="11" t="n">
-        <v>117.45</v>
+        <v>103.57</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>122.71</v>
+        <v>90.12</v>
       </c>
       <c r="T33" s="13" t="n">
-        <v>15268</v>
+        <v>20196</v>
       </c>
       <c r="U33" s="13" t="n">
-        <v>15952</v>
+        <v>17573</v>
       </c>
       <c r="V33" s="14" t="n">
-        <v>607</v>
+        <v>-2704</v>
       </c>
       <c r="W33" s="15" t="n">
-        <v>4</v>
+        <v>-13.4</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y33" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z33" s="10" t="inlineStr">
         <is>
-          <t>13:25 trendline breakdown: 5m close 23,245.00 below ascending line 23,252.00 (slope +2.86) | Anchored by swing lows at 12:00 (23,206.20) and 13:00 (23,240.55)</t>
+          <t>11:40 trendline breakout: 5m close 22,558.75 above descending line 22,551.28 (slope -3.59) | Anchored by swing highs at 10:35 (22,594.40) and 11:15 (22,565.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3977,77 +3977,77 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.86R)</t>
+          <t>TRAILED (+0.23R)</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>23326.7</v>
+        <v>22670.3</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>23358.9</v>
+        <v>22636.25</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23235.25</v>
+        <v>22772.45</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>32.2</v>
+        <v>34.05</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>23271.35</v>
+        <v>22678</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Partial + Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N34" s="4" t="n">
-        <v>55.35</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>1.86</v>
+        <v>7.7</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>0.23</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23250 PE</t>
+          <t>NIFTY 22750 CE</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R34" s="4" t="n">
-        <v>124.18</v>
+        <v>150.92</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>148.27</v>
+        <v>153.99</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>32287</v>
+        <v>39239</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>38550</v>
-      </c>
-      <c r="V34" s="7" t="n">
-        <v>6147</v>
-      </c>
-      <c r="W34" s="8" t="n">
-        <v>19</v>
+        <v>40037</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>677</v>
+      </c>
+      <c r="W34" s="18" t="n">
+        <v>1.7</v>
       </c>
       <c r="X34" s="2" t="n">
         <v>4</v>
@@ -4057,19 +4057,19 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>12:20 trendline breakdown: 5m close 23,326.70 below ascending line 23,329.24 (slope +1.94) | Anchored by swing lows at 11:30 (23,311.80) and 11:50 (23,319.55) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>10:40 trendline breakout: 5m close 22,670.30 above descending line 22,660.45 (slope -0.86) | Anchored by swing highs at 09:55 (22,667.35) and 10:15 (22,663.90)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -4089,89 +4089,89 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.44R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G35" s="11" t="n">
-        <v>23437.8</v>
+        <v>22689.75</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>23470.2</v>
+        <v>22728.7</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>23340.6</v>
+        <v>22564.8</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>32.4</v>
+        <v>38.95</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>23391</v>
+        <v>22703.35</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N35" s="11" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>1.44</v>
+        <v>-13.6</v>
+      </c>
+      <c r="O35" s="22" t="n">
+        <v>-0.35</v>
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23350 PE</t>
+          <t>NIFTY 22600 PE</t>
         </is>
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R35" s="11" t="n">
-        <v>92.29000000000001</v>
+        <v>144.03</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>110.78</v>
+        <v>138.09</v>
       </c>
       <c r="T35" s="13" t="n">
-        <v>11998</v>
+        <v>37448</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>14401</v>
+        <v>35903</v>
       </c>
       <c r="V35" s="14" t="n">
-        <v>2331</v>
+        <v>-1659</v>
       </c>
       <c r="W35" s="15" t="n">
-        <v>19.4</v>
+        <v>-4.4</v>
       </c>
       <c r="X35" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z35" s="10" t="inlineStr">
         <is>
-          <t>13:00 trendline breakdown: 5m close 23,437.80 below ascending line 23,452.19 (slope +3.12) | Anchored by swing lows at 11:40 (23,405.35) and 12:35 (23,439.70) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>14:30 trendline breakdown: 5m close 22,689.75 below ascending line 22,712.70 (slope +1.79) | Anchored by swing lows at 13:25 (22,691.25) and 13:45 (22,698.40)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4191,67 +4191,67 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>23431.8</v>
+        <v>22713.3</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>23400.35</v>
+        <v>22674.75</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>23486.7</v>
+        <v>22828.95</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>31.45</v>
+        <v>38.55</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>23431.8</v>
+        <v>22674.75</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>0</v>
+        <v>-38.55</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23550 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R36" s="4" t="n">
-        <v>81.92</v>
+        <v>120.65</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>105.17</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>15974</v>
+        <v>23527</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>15842</v>
-      </c>
-      <c r="V36" s="17" t="n">
-        <v>-209</v>
-      </c>
-      <c r="W36" s="18" t="n">
-        <v>-1.3</v>
+        <v>20508</v>
+      </c>
+      <c r="V36" s="7" t="n">
+        <v>-3105</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>-13.2</v>
       </c>
       <c r="X36" s="2" t="n">
         <v>3</v>
@@ -4261,19 +4261,19 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>11:50 trendline breakout: 5m close 23,431.80 above descending line 23,431.30 (slope -2.58) | Anchored by swing highs at 11:15 (23,446.80) and 11:30 (23,439.05) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:05 trendline breakout: 5m close 22,713.30 above descending line 22,685.03 (slope -2.33) | Anchored by swing highs at 11:05 (22,710.70) and 11:35 (22,696.70) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -4293,89 +4293,89 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.40R)</t>
         </is>
       </c>
       <c r="G37" s="11" t="n">
-        <v>23502.35</v>
+        <v>22674.9</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>23537.35</v>
+        <v>22722.25</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>23397.35</v>
+        <v>22588.4</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>35</v>
+        <v>47.35</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>23537.35</v>
+        <v>22656.15</v>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N37" s="11" t="n">
-        <v>-35</v>
-      </c>
-      <c r="O37" s="23" t="n">
-        <v>-1</v>
+        <v>18.75</v>
+      </c>
+      <c r="O37" s="19" t="n">
+        <v>0.4</v>
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23400 PE</t>
+          <t>NIFTY 22550 PE</t>
         </is>
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R37" s="11" t="n">
-        <v>91.26000000000001</v>
+        <v>104.46</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>78.37</v>
+        <v>111.34</v>
       </c>
       <c r="T37" s="13" t="n">
-        <v>11864</v>
+        <v>20370</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>10188</v>
+        <v>21711</v>
       </c>
       <c r="V37" s="20" t="n">
-        <v>-1743</v>
+        <v>1255</v>
       </c>
       <c r="W37" s="21" t="n">
-        <v>-14.7</v>
+        <v>6.2</v>
       </c>
       <c r="X37" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y37" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z37" s="10" t="inlineStr">
         <is>
-          <t>11:55 trendline breakdown: 5m close 23,502.35 below ascending line 23,518.71 (slope +1.22) | Anchored by swing lows at 10:40 (23,501.60) and 11:25 (23,512.60) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:15 trendline breakdown: 5m close 22,674.90 below ascending line 22,683.45 (slope +3.05) | Anchored by swing lows at 11:30 (22,659.05) and 11:45 (22,668.20) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4395,89 +4395,89 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.69R)</t>
+          <t>TRAILED (+0.31R)</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>23670.35</v>
+        <v>22460.8</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>23703.6</v>
+        <v>22503.1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>23570.6</v>
+        <v>22333.9</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>33.25</v>
+        <v>42.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>23647.3</v>
+        <v>22447.6</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>23.05</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.2</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>0.31</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23550 PE</t>
+          <t>NIFTY 22350 PE</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R38" s="4" t="n">
-        <v>95.08</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>102.14</v>
+        <v>104.31</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>24721</v>
+        <v>19410</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>26556</v>
-      </c>
-      <c r="V38" s="7" t="n">
-        <v>1740</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>7</v>
+        <v>20340</v>
+      </c>
+      <c r="V38" s="17" t="n">
+        <v>846</v>
+      </c>
+      <c r="W38" s="18" t="n">
+        <v>4.4</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>11:00 trendline breakdown: 5m close 23,670.35 below ascending line 23,672.27 (slope +1.51) | Anchored by swing lows at 10:05 (23,657.20) and 10:40 (23,667.75)</t>
+          <t>10:20 trendline breakdown: 5m close 22,460.80 below ascending line 22,467.75 (slope +3.68) | Anchored by swing lows at 09:45 (22,445.70) and 10:05 (22,460.40)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -4497,89 +4497,89 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.54R)</t>
+          <t>FLAT</t>
         </is>
       </c>
       <c r="G39" s="11" t="n">
-        <v>23959.1</v>
+        <v>22486.7</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>23996.75</v>
+        <v>22522.6</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>23876.45</v>
+        <v>22325.15</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>37.65</v>
+        <v>35.9</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>23938.6</v>
+        <v>22486.7</v>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Breakeven</t>
         </is>
       </c>
       <c r="N39" s="11" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>0.54</v>
+        <v>-0</v>
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23850 PE</t>
+          <t>NIFTY 22400 PE</t>
         </is>
       </c>
       <c r="Q39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R39" s="11" t="n">
-        <v>68.78</v>
+        <v>106.72</v>
       </c>
       <c r="S39" s="11" t="n">
-        <v>74.52</v>
+        <v>106.42</v>
       </c>
       <c r="T39" s="13" t="n">
-        <v>8941</v>
+        <v>20810</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>9688</v>
+        <v>20752</v>
       </c>
       <c r="V39" s="14" t="n">
-        <v>681</v>
+        <v>-144</v>
       </c>
       <c r="W39" s="15" t="n">
-        <v>7.6</v>
+        <v>-0.7</v>
       </c>
       <c r="X39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y39" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z39" s="10" t="inlineStr">
         <is>
-          <t>12:05 trendline breakdown: 5m close 23,959.10 below ascending line 23,974.68 (slope +1.53) | Anchored by swing lows at 10:45 (23,951.80) and 11:15 (23,960.95) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:45 trendline breakdown: 5m close 22,486.70 below ascending line 22,489.01 (slope +1.26) | Anchored by swing lows at 10:35 (22,472.65) and 11:05 (22,480.20) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4599,27 +4599,27 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.17R)</t>
+          <t>TRAILED (+0.71R)</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>23838.35</v>
+        <v>22526.15</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>23796.1</v>
+        <v>22490.25</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>23949.6</v>
+        <v>22596.05</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>42.25</v>
+        <v>35.9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>23887.65</v>
+        <v>22551.65</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4628,60 +4628,60 @@
         </is>
       </c>
       <c r="N40" s="4" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>1.17</v>
+        <v>25.5</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0.71</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23950 CE</t>
+          <t>NIFTY 22650 CE</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R40" s="4" t="n">
-        <v>93.11</v>
+        <v>91.84</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>111.95</v>
+        <v>101.07</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>12104</v>
+        <v>17909</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>14554</v>
-      </c>
-      <c r="V40" s="7" t="n">
-        <v>2376</v>
-      </c>
-      <c r="W40" s="8" t="n">
-        <v>19.6</v>
+        <v>19709</v>
+      </c>
+      <c r="V40" s="17" t="n">
+        <v>1717</v>
+      </c>
+      <c r="W40" s="18" t="n">
+        <v>9.6</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>12:15 trendline breakout: 5m close 23,838.35 above descending line 23,820.60 (slope -3.18) | Anchored by swing highs at 10:50 (23,871.55) and 11:55 (23,830.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:45 trendline breakout: 5m close 22,526.15 above descending line 22,509.90 (slope -0.60) | Anchored by swing highs at 12:55 (22,515.30) and 13:20 (22,512.30)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -4701,89 +4701,89 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.21R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G41" s="11" t="n">
-        <v>24093.5</v>
+        <v>22363</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>24123.7</v>
+        <v>22413.65</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>24028.55</v>
+        <v>22211.05</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>30.2</v>
+        <v>50.65</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>24056.9</v>
+        <v>22374.7</v>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N41" s="11" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="O41" s="12" t="n">
-        <v>1.21</v>
+        <v>-11.7</v>
+      </c>
+      <c r="O41" s="22" t="n">
+        <v>-0.23</v>
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24000 PE</t>
+          <t>NIFTY 22250 PE</t>
         </is>
       </c>
       <c r="Q41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R41" s="11" t="n">
-        <v>107.67</v>
+        <v>27.58</v>
       </c>
       <c r="S41" s="11" t="n">
-        <v>122.74</v>
+        <v>24.07</v>
       </c>
       <c r="T41" s="13" t="n">
-        <v>27994</v>
+        <v>5378</v>
       </c>
       <c r="U41" s="13" t="n">
-        <v>31912</v>
+        <v>4694</v>
       </c>
       <c r="V41" s="14" t="n">
-        <v>3813</v>
+        <v>-741</v>
       </c>
       <c r="W41" s="15" t="n">
-        <v>13.6</v>
+        <v>-13.8</v>
       </c>
       <c r="X41" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y41" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z41" s="10" t="inlineStr">
         <is>
-          <t>12:55 trendline breakdown: 5m close 24,093.50 below ascending line 24,103.23 (slope +1.72) | Anchored by swing lows at 10:40 (24,058.60) and 12:25 (24,094.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:15 trendline breakdown: 5m close 22,363.00 below ascending line 22,374.22 (slope +1.81) | Anchored by swing lows at 12:10 (22,352.55) and 12:50 (22,367.00)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4807,23 +4807,23 @@
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>24174.25</v>
+        <v>22557.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>24136.7</v>
+        <v>22525.3</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>24293.9</v>
+        <v>22647.55</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>37.55</v>
+        <v>32.2</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>24136.7</v>
+        <v>22525.3</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -4832,60 +4832,60 @@
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>-37.55</v>
-      </c>
-      <c r="O42" s="22" t="n">
+        <v>-32.2</v>
+      </c>
+      <c r="O42" s="5" t="n">
         <v>-1</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24250 CE</t>
+          <t>NIFTY 22650 CE</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R42" s="4" t="n">
-        <v>86.78</v>
+        <v>135.25</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>71.98</v>
+        <v>122.03</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>11281</v>
+        <v>35165</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>9357</v>
-      </c>
-      <c r="V42" s="17" t="n">
-        <v>-1989</v>
-      </c>
-      <c r="W42" s="18" t="n">
-        <v>-17.6</v>
+        <v>31728</v>
+      </c>
+      <c r="V42" s="7" t="n">
+        <v>-3545</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>-10.1</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>12:40 trendline breakout: 5m close 24,174.25 above descending line 24,159.12 (slope -0.53) | Anchored by swing highs at 11:05 (24,168.75) and 11:55 (24,163.40) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>13:15 trendline breakout: 5m close 22,557.50 above descending line 22,550.30 (slope -0.95) | Anchored by swing highs at 12:30 (22,557.90) and 12:50 (22,554.10)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -4905,89 +4905,89 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.34R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G43" s="11" t="n">
-        <v>24177.3</v>
+        <v>22744.6</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>24123.95</v>
+        <v>22707.85</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>24309.85</v>
+        <v>22854.85</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>53.35</v>
+        <v>36.75</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>24248.65</v>
+        <v>22707.85</v>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N43" s="11" t="n">
-        <v>71.34999999999999</v>
-      </c>
-      <c r="O43" s="12" t="n">
-        <v>1.34</v>
+        <v>-36.75</v>
+      </c>
+      <c r="O43" s="22" t="n">
+        <v>-1</v>
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24300 CE</t>
+          <t>NIFTY 22850 CE</t>
         </is>
       </c>
       <c r="Q43" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R43" s="11" t="n">
-        <v>101.43</v>
+        <v>106.13</v>
       </c>
       <c r="S43" s="11" t="n">
-        <v>130.46</v>
+        <v>92.19</v>
       </c>
       <c r="T43" s="13" t="n">
-        <v>26372</v>
+        <v>20695</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>33920</v>
+        <v>17977</v>
       </c>
       <c r="V43" s="14" t="n">
-        <v>7441</v>
+        <v>-2800</v>
       </c>
       <c r="W43" s="15" t="n">
-        <v>28.2</v>
+        <v>-13.5</v>
       </c>
       <c r="X43" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y43" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z43" s="10" t="inlineStr">
         <is>
-          <t>13:55 trendline breakout: 5m close 24,177.30 above descending line 24,137.15 (slope -2.30) | Anchored by swing highs at 11:55 (24,189.95) and 12:55 (24,162.40)</t>
+          <t>11:00 trendline breakout: 5m close 22,744.60 above descending line 22,738.33 (slope -1.39) | Anchored by swing highs at 09:45 (22,757.80) and 10:40 (22,742.50)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5007,89 +5007,89 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>TRAILED (+1.87R)</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>24285.5</v>
+        <v>22975.1</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>24251.55</v>
+        <v>22941.5</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24354.6</v>
+        <v>23075.9</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>33.95</v>
+        <v>33.6</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>24354.6</v>
+        <v>23033.5</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Partial + Structure Trail</t>
         </is>
       </c>
       <c r="N44" s="4" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>2.02</v>
+        <v>58.4</v>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>1.87</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24400 CE</t>
+          <t>NIFTY 23100 CE</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R44" s="4" t="n">
-        <v>20.22</v>
+        <v>89.03</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>40.12</v>
+        <v>111.19</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>5257</v>
+        <v>17361</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>10431</v>
-      </c>
-      <c r="V44" s="7" t="n">
-        <v>5110</v>
-      </c>
-      <c r="W44" s="8" t="n">
-        <v>97.2</v>
+        <v>21682</v>
+      </c>
+      <c r="V44" s="17" t="n">
+        <v>4236</v>
+      </c>
+      <c r="W44" s="18" t="n">
+        <v>24.4</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>12:20 trendline breakout: 5m close 24,285.50 above descending line 24,271.71 (slope -1.31) | Anchored by swing highs at 09:40 (24,312.45) and 12:00 (24,275.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -5099,99 +5099,99 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.39R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G45" s="11" t="n">
-        <v>24357.35</v>
+        <v>23096.8</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>24322.35</v>
+        <v>23141.15</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>24425.9</v>
+        <v>22917.3</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>35</v>
+        <v>44.35</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>24371.05</v>
+        <v>23141.15</v>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N45" s="11" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="O45" s="12" t="n">
-        <v>0.39</v>
+        <v>-44.35</v>
+      </c>
+      <c r="O45" s="22" t="n">
+        <v>-1</v>
       </c>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24450 CE</t>
+          <t>NIFTY 23000 PE</t>
         </is>
       </c>
       <c r="Q45" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R45" s="11" t="n">
-        <v>76.89</v>
+        <v>76.78</v>
       </c>
       <c r="S45" s="11" t="n">
-        <v>81.38</v>
+        <v>61.28</v>
       </c>
       <c r="T45" s="13" t="n">
-        <v>9996</v>
+        <v>14972</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>10579</v>
+        <v>11950</v>
       </c>
       <c r="V45" s="14" t="n">
-        <v>517</v>
+        <v>-3093</v>
       </c>
       <c r="W45" s="15" t="n">
-        <v>5.2</v>
+        <v>-20.7</v>
       </c>
       <c r="X45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y45" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z45" s="10" t="inlineStr">
         <is>
-          <t>13:45 trendline breakout: 5m close 24,357.35 above descending line 24,345.88 (slope -0.59) | Anchored by swing highs at 12:25 (24,354.65) and 13:15 (24,348.80)</t>
+          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5215,23 +5215,23 @@
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>24334.05</v>
+        <v>22573.4</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>24364.2</v>
+        <v>22617.45</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>24243.6</v>
+        <v>22390.45</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>30.15</v>
+        <v>44.05</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>24334.05</v>
+        <v>22573.4</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5242,36 +5242,36 @@
       <c r="N46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="16" t="n">
+      <c r="O46" s="23" t="n">
         <v>-0</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24250 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R46" s="4" t="n">
-        <v>81.56</v>
+        <v>37.68</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>81.31999999999999</v>
+        <v>37.25</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>15904</v>
+        <v>7348</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>15857</v>
-      </c>
-      <c r="V46" s="17" t="n">
-        <v>-124</v>
-      </c>
-      <c r="W46" s="18" t="n">
-        <v>-0.8</v>
+        <v>7264</v>
+      </c>
+      <c r="V46" s="7" t="n">
+        <v>-145</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>-2</v>
       </c>
       <c r="X46" s="2" t="n">
         <v>3</v>
@@ -5281,19 +5281,19 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>10:25 trendline breakdown: 5m close 24,334.05 below ascending line 24,340.50 (slope +3.59) | Anchored by swing lows at 09:30 (24,304.60) and 09:55 (24,322.55)</t>
+          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -5303,99 +5303,99 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>FLAT</t>
         </is>
       </c>
       <c r="G47" s="11" t="n">
-        <v>24585.4</v>
+        <v>22781.5</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>24615.45</v>
+        <v>22744.75</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>24525.9</v>
+        <v>22891.75</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>30.05</v>
+        <v>36.75</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>24615.45</v>
+        <v>22781.5</v>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Breakeven</t>
         </is>
       </c>
       <c r="N47" s="11" t="n">
-        <v>-30.05</v>
-      </c>
-      <c r="O47" s="23" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="O47" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24500 PE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q47" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R47" s="11" t="n">
-        <v>32.97</v>
+        <v>164.2</v>
       </c>
       <c r="S47" s="11" t="n">
-        <v>23.99</v>
+        <v>164.05</v>
       </c>
       <c r="T47" s="13" t="n">
-        <v>6429</v>
+        <v>42692</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>4678</v>
-      </c>
-      <c r="V47" s="20" t="n">
-        <v>-1808</v>
-      </c>
-      <c r="W47" s="21" t="n">
-        <v>-28.1</v>
+        <v>42653</v>
+      </c>
+      <c r="V47" s="14" t="n">
+        <v>-166</v>
+      </c>
+      <c r="W47" s="15" t="n">
+        <v>-0.4</v>
       </c>
       <c r="X47" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y47" s="9" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z47" s="10" t="inlineStr">
         <is>
-          <t>11:35 trendline breakdown: 5m close 24,585.40 below ascending line 24,601.97 (slope +3.94) | Anchored by swing lows at 09:35 (24,511.30) and 11:10 (24,586.20) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5415,89 +5415,89 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+1.05R)</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>24538.2</v>
+        <v>22736.1</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>24584.65</v>
+        <v>22790.35</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24398.85</v>
+        <v>22491.97</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>46.45</v>
+        <v>54.25</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>24553.9</v>
+        <v>22678.95</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N48" s="4" t="n">
-        <v>-15.7</v>
-      </c>
-      <c r="O48" s="22" t="n">
-        <v>-0.34</v>
+        <v>57.15</v>
+      </c>
+      <c r="O48" s="16" t="n">
+        <v>1.05</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24450 PE</t>
+          <t>NIFTY 22650 PE</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R48" s="4" t="n">
-        <v>86.06</v>
+        <v>176.29</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>79.52</v>
+        <v>201.28</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>11188</v>
+        <v>45835</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>10338</v>
+        <v>52333</v>
       </c>
       <c r="V48" s="17" t="n">
-        <v>-917</v>
+        <v>6356</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>-8.199999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
-          <t>14:10 trendline breakdown: 5m close 24,538.20 below ascending line 24,550.02 (slope +0.78) | Anchored by swing lows at 12:15 (24,532.90) and 13:35 (24,545.35)</t>
+          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -5517,89 +5517,89 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.16R)</t>
         </is>
       </c>
       <c r="G49" s="11" t="n">
-        <v>24652.45</v>
+        <v>22610.25</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>24616.6</v>
+        <v>22575.35</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>24760</v>
+        <v>22686.15</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>35.85</v>
+        <v>34.9</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>24616.6</v>
+        <v>22615.85</v>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N49" s="11" t="n">
-        <v>-35.85</v>
-      </c>
-      <c r="O49" s="23" t="n">
-        <v>-1</v>
+        <v>5.6</v>
+      </c>
+      <c r="O49" s="19" t="n">
+        <v>0.16</v>
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24750 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q49" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R49" s="11" t="n">
-        <v>98.08</v>
+        <v>151.21</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>83.52</v>
+        <v>153.26</v>
       </c>
       <c r="T49" s="13" t="n">
-        <v>12750</v>
+        <v>29486</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>10858</v>
+        <v>29886</v>
       </c>
       <c r="V49" s="20" t="n">
-        <v>-1961</v>
+        <v>297</v>
       </c>
       <c r="W49" s="21" t="n">
-        <v>-15.4</v>
+        <v>1</v>
       </c>
       <c r="X49" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y49" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z49" s="10" t="inlineStr">
         <is>
-          <t>11:15 trendline breakout: 5m close 24,652.45 above descending line 24,638.54 (slope -0.69) | Anchored by swing highs at 10:35 (24,643.35) and 10:55 (24,640.60)</t>
+          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5609,87 +5609,87 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Micro Trendline Breakdown [1M Micro-Execution]</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+1.00R)</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>24609.4</v>
+        <v>22852.55</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>24570.1</v>
+        <v>22873</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>24727.3</v>
+        <v>22780.85</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>39.3</v>
+        <v>20.45</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>24609.4</v>
+        <v>22828</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Trailed Stop Hit (+1.0R Locked)</t>
         </is>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24700 CE</t>
+          <t>NIFTY 22750 PE</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R50" s="4" t="n">
-        <v>115.06</v>
+        <v>102.37</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>114.72</v>
+        <v>110.02</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>14958</v>
+        <v>26616</v>
       </c>
       <c r="U50" s="6" t="n">
-        <v>14914</v>
+        <v>28605</v>
       </c>
       <c r="V50" s="17" t="n">
-        <v>-119</v>
+        <v>1989</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>-0.8</v>
+        <v>7.5</v>
       </c>
       <c r="X50" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y50" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
-          <t>10:50 trendline breakout: 5m close 24,609.40 above descending line 24,608.33 (slope -2.12) | Anchored by swing highs at 09:40 (24,635.95) and 10:10 (24,623.20)</t>
+          <t>10:36 1M CHoCH breakdown of ascending trendline below VWAP. Trailed stop hit at 11:14 IST after +2R milestone reached.</t>
         </is>
       </c>
     </row>
